--- a/public/report/YearReport.xlsx
+++ b/public/report/YearReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Test\19-5Restful+API\RestfulAPI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD006E39-8AA3-46E0-9354-E6943D6B2AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF13383-BBD7-4F49-8433-3E15B31042E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="年報" sheetId="3" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>充放電效率
 (%)</t>
@@ -96,13 +96,6 @@
   </si>
   <si>
     <t>Minute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>###</t>
-  </si>
-  <si>
-    <t>###</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1572,42 +1565,6 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>87.17386338079298</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>92.586446890890713</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>91.746563242772112</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>90.999999999999957</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>89.600193919802322</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>90.999999999999957</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>90.533397973267441</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>90.999999999999957</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>90.833481868311836</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>90.999999999999957</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>88.200387839604616</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>92.866408106930251</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3221,7 +3178,7 @@
     <row r="2" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
@@ -3239,7 +3196,7 @@
     </row>
     <row r="4" spans="3:16" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="57" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" s="59" t="s">
         <v>1</v>
@@ -3262,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3307,654 +3264,292 @@
       <c r="C6" s="12">
         <v>1</v>
       </c>
-      <c r="D6" s="13">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0</v>
-      </c>
-      <c r="I6" s="14">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="39">
-        <v>0</v>
-      </c>
-      <c r="L6" s="16">
-        <v>1071.577</v>
-      </c>
-      <c r="M6" s="17">
-        <v>934.13507000000004</v>
-      </c>
-      <c r="N6" s="47">
-        <f>L6-M6</f>
-        <v>137.44192999999996</v>
-      </c>
-      <c r="O6" s="41">
-        <f>M6/L6*100</f>
-        <v>87.17386338079298</v>
-      </c>
-      <c r="P6" s="23">
-        <v>3.6</v>
-      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="23"/>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C7" s="11">
         <v>2</v>
       </c>
-      <c r="D7" s="13">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="40">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M7" s="4">
-        <v>992.13507000000004</v>
-      </c>
-      <c r="N7" s="48">
-        <f t="shared" ref="N7:N17" si="0">L7-M7</f>
-        <v>79.441929999999957</v>
-      </c>
-      <c r="O7" s="42">
-        <f>M7/L7*100</f>
-        <v>92.586446890890713</v>
-      </c>
-      <c r="P7" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="24"/>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C8" s="11">
         <v>3</v>
       </c>
-      <c r="D8" s="13">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>0</v>
-      </c>
-      <c r="I8" s="14">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="40">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M8" s="4">
-        <v>983.13507000000004</v>
-      </c>
-      <c r="N8" s="48">
-        <f t="shared" si="0"/>
-        <v>88.441929999999957</v>
-      </c>
-      <c r="O8" s="42">
-        <f t="shared" ref="O8:O18" si="1">M8/L8*100</f>
-        <v>91.746563242772112</v>
-      </c>
-      <c r="P8" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="24"/>
     </row>
     <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9" s="11">
         <v>4</v>
       </c>
-      <c r="D9" s="13">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14">
-        <v>0</v>
-      </c>
-      <c r="I9" s="14">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="40">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M9" s="4">
-        <v>975.13506999999959</v>
-      </c>
-      <c r="N9" s="48">
-        <f t="shared" si="0"/>
-        <v>96.441930000000411</v>
-      </c>
-      <c r="O9" s="42">
-        <f t="shared" si="1"/>
-        <v>90.999999999999957</v>
-      </c>
-      <c r="P9" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="24"/>
     </row>
     <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10" s="11">
         <v>5</v>
       </c>
-      <c r="D10" s="13">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0</v>
-      </c>
-      <c r="H10" s="14">
-        <v>0</v>
-      </c>
-      <c r="I10" s="14">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="40">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M10" s="4">
-        <v>960.13507000000004</v>
-      </c>
-      <c r="N10" s="48">
-        <f t="shared" si="0"/>
-        <v>111.44192999999996</v>
-      </c>
-      <c r="O10" s="42">
-        <f t="shared" si="1"/>
-        <v>89.600193919802322</v>
-      </c>
-      <c r="P10" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="24"/>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C11" s="11">
         <v>6</v>
       </c>
-      <c r="D11" s="13">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14">
-        <v>0</v>
-      </c>
-      <c r="I11" s="14">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-      <c r="K11" s="40">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M11" s="4">
-        <v>975.13506999999959</v>
-      </c>
-      <c r="N11" s="48">
-        <f t="shared" si="0"/>
-        <v>96.441930000000411</v>
-      </c>
-      <c r="O11" s="42">
-        <f t="shared" si="1"/>
-        <v>90.999999999999957</v>
-      </c>
-      <c r="P11" s="36">
-        <v>3.6</v>
-      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="36"/>
     </row>
     <row r="12" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C12" s="11">
         <v>7</v>
       </c>
-      <c r="D12" s="13">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14">
-        <v>0</v>
-      </c>
-      <c r="H12" s="14">
-        <v>0</v>
-      </c>
-      <c r="I12" s="14">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="40">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M12" s="4">
-        <v>970.13507000000004</v>
-      </c>
-      <c r="N12" s="48">
-        <f t="shared" si="0"/>
-        <v>101.44192999999996</v>
-      </c>
-      <c r="O12" s="42">
-        <f t="shared" si="1"/>
-        <v>90.533397973267441</v>
-      </c>
-      <c r="P12" s="25">
-        <v>3.6</v>
-      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="25"/>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C13" s="11">
         <v>8</v>
       </c>
-      <c r="D13" s="13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14">
-        <v>0</v>
-      </c>
-      <c r="I13" s="14">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="40">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M13" s="4">
-        <v>975.13506999999959</v>
-      </c>
-      <c r="N13" s="48">
-        <f t="shared" si="0"/>
-        <v>96.441930000000411</v>
-      </c>
-      <c r="O13" s="42">
-        <f t="shared" si="1"/>
-        <v>90.999999999999957</v>
-      </c>
-      <c r="P13" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="24"/>
     </row>
     <row r="14" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C14" s="11">
         <v>9</v>
       </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>0</v>
-      </c>
-      <c r="I14" s="14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-      <c r="K14" s="40">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M14" s="4">
-        <v>973.35069999999996</v>
-      </c>
-      <c r="N14" s="48">
-        <f t="shared" si="0"/>
-        <v>98.226300000000037</v>
-      </c>
-      <c r="O14" s="42">
-        <f t="shared" si="1"/>
-        <v>90.833481868311836</v>
-      </c>
-      <c r="P14" s="36">
-        <v>3.6</v>
-      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="36"/>
     </row>
     <row r="15" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C15" s="11">
         <v>10</v>
       </c>
-      <c r="D15" s="13">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
-      </c>
-      <c r="I15" s="14">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="40">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M15" s="4">
-        <v>975.13506999999959</v>
-      </c>
-      <c r="N15" s="48">
-        <f t="shared" si="0"/>
-        <v>96.441930000000411</v>
-      </c>
-      <c r="O15" s="42">
-        <f t="shared" si="1"/>
-        <v>90.999999999999957</v>
-      </c>
-      <c r="P15" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="24"/>
     </row>
     <row r="16" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C16" s="11">
         <v>11</v>
       </c>
-      <c r="D16" s="13">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-      <c r="K16" s="40">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10">
-        <v>1071.577</v>
-      </c>
-      <c r="M16" s="4">
-        <v>945.13507000000004</v>
-      </c>
-      <c r="N16" s="48">
-        <f t="shared" si="0"/>
-        <v>126.44192999999996</v>
-      </c>
-      <c r="O16" s="42">
-        <f t="shared" si="1"/>
-        <v>88.200387839604616</v>
-      </c>
-      <c r="P16" s="24">
-        <v>3.6</v>
-      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="24"/>
     </row>
     <row r="17" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="11">
         <v>12</v>
       </c>
-      <c r="D17" s="13">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="14">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0</v>
-      </c>
-      <c r="H17" s="14">
-        <v>0</v>
-      </c>
-      <c r="I17" s="14">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-      <c r="K17" s="40">
-        <v>0</v>
-      </c>
-      <c r="L17" s="49">
-        <v>1071.577</v>
-      </c>
-      <c r="M17" s="50">
-        <v>995.13507000000004</v>
-      </c>
-      <c r="N17" s="51">
-        <f t="shared" si="0"/>
-        <v>76.441929999999957</v>
-      </c>
-      <c r="O17" s="42">
-        <f t="shared" si="1"/>
-        <v>92.866408106930251</v>
-      </c>
-      <c r="P17" s="38">
-        <v>3.6</v>
-      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="38"/>
     </row>
     <row r="18" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C18" s="27" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="28">
-        <f t="shared" ref="D18:N18" si="2">SUM(D6:D17)</f>
+        <f t="shared" ref="D18:N18" si="0">SUM(D6:D17)</f>
         <v>0</v>
       </c>
       <c r="E18" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F18" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G18" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H18" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I18" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J18" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K18" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L18" s="33">
-        <f t="shared" si="2"/>
-        <v>12858.923999999997</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M18" s="34">
-        <f t="shared" si="2"/>
-        <v>11653.836469999998</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="N18" s="46">
-        <f t="shared" si="2"/>
-        <v>1205.0875300000014</v>
-      </c>
-      <c r="O18" s="32">
-        <f t="shared" si="1"/>
-        <v>90.628395268531023</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="32" t="e">
+        <f t="shared" ref="O8:O18" si="1">M18/L18*100</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="P18" s="26">
         <f>SUM(P6:P17)</f>
-        <v>43.20000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="M19" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="N19" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="O19" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="P19" s="37" t="s">
-        <v>10</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/public/report/YearReport.xlsx
+++ b/public/report/YearReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF13383-BBD7-4F49-8433-3E15B31042E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAA5ACF-F9B9-4FC4-B8B6-27F67BB74514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="年報" sheetId="3" r:id="rId1"/>
@@ -38,29 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={F6C53C23-FFA1-4362-A18B-75EA2901F729}</author>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{F6C53C23-FFA1-4362-A18B-75EA2901F729}">
-      <text>
-        <t>[對話串註解]
-您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
-註解:
-    XX=縣市
-YY=地區
-ZZ=併網容量
-e.g. 花蓮和平10MW</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>充放電效率
 (%)</t>
@@ -99,78 +78,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>XXYYZZ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">MW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>E-dReg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>AA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 年報</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>月
 (Day)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -184,6 +91,18 @@
 (MWh)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>花蓮和平10MW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-dReg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年報</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -193,7 +112,7 @@
     <numFmt numFmtId="176" formatCode="0.0_ "/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,19 +141,6 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -244,7 +150,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -513,19 +419,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -783,6 +676,65 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -825,10 +777,10 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -855,22 +807,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -882,43 +834,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -927,65 +876,64 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2881,9 +2829,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="星佑_整合EMS處 羅胤恆" id="{B8A74333-F443-456F-BDB7-E92946D76E41}" userId="S::steven.lo@hdrenewables.com::5cc4d8c8-8edb-4dcf-9121-6fa7b0de8500" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3147,19 +3093,8 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C3" dT="2023-11-27T08:34:48.63" personId="{B8A74333-F443-456F-BDB7-E92946D76E41}" id="{F6C53C23-FFA1-4362-A18B-75EA2901F729}">
-    <text>XX=縣市
-YY=地區
-ZZ=併網容量
-e.g. 花蓮和平10MW</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2222E726-C907-436C-820E-D25BB221BFD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2222E726-C907-436C-820E-D25BB221BFD8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3177,53 +3112,57 @@
   <sheetData>
     <row r="2" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54" t="s">
+        <v>13</v>
+      </c>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
       <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="27"/>
+      <c r="M3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="64"/>
     </row>
     <row r="4" spans="3:16" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="59" t="s">
+      <c r="C4" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="21" t="s">
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="57" t="s">
+      <c r="L4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63" t="s">
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="P4" s="52" t="s">
-        <v>12</v>
+      <c r="P4" s="51" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="58"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="6">
         <v>1</v>
       </c>
@@ -3248,17 +3187,17 @@
       <c r="K5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="M5" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="45" t="s">
+      <c r="N5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="O5" s="64"/>
-      <c r="P5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="51"/>
     </row>
     <row r="6" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C6" s="12">
@@ -3271,12 +3210,12 @@
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="9"/>
-      <c r="K6" s="39"/>
+      <c r="K6" s="38"/>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="23"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="22"/>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C7" s="11">
@@ -3289,12 +3228,12 @@
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="40"/>
+      <c r="K7" s="39"/>
       <c r="L7" s="10"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="24"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="23"/>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C8" s="11">
@@ -3307,12 +3246,12 @@
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="40"/>
+      <c r="K8" s="39"/>
       <c r="L8" s="10"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="24"/>
+      <c r="N8" s="47"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="23"/>
     </row>
     <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9" s="11">
@@ -3325,12 +3264,12 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="40"/>
+      <c r="K9" s="39"/>
       <c r="L9" s="10"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="24"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="23"/>
     </row>
     <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10" s="11">
@@ -3343,12 +3282,12 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="40"/>
+      <c r="K10" s="39"/>
       <c r="L10" s="10"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="24"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="23"/>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C11" s="11">
@@ -3361,12 +3300,12 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="40"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="10"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="36"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="35"/>
     </row>
     <row r="12" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C12" s="11">
@@ -3379,12 +3318,12 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="40"/>
+      <c r="K12" s="39"/>
       <c r="L12" s="10"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="25"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="24"/>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C13" s="11">
@@ -3397,12 +3336,12 @@
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="40"/>
+      <c r="K13" s="39"/>
       <c r="L13" s="10"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="24"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="23"/>
     </row>
     <row r="14" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C14" s="11">
@@ -3415,12 +3354,12 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="40"/>
+      <c r="K14" s="39"/>
       <c r="L14" s="10"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="36"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="35"/>
     </row>
     <row r="15" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C15" s="11">
@@ -3433,12 +3372,12 @@
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="40"/>
+      <c r="K15" s="39"/>
       <c r="L15" s="10"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="24"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="23"/>
     </row>
     <row r="16" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C16" s="11">
@@ -3451,12 +3390,12 @@
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="40"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="10"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="24"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="23"/>
     </row>
     <row r="17" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="11">
@@ -3469,73 +3408,73 @@
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="5"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="38"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="37"/>
     </row>
     <row r="18" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f t="shared" ref="D18:N18" si="0">SUM(D6:D17)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="33">
+      <c r="L18" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N18" s="46">
+      <c r="N18" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O18" s="32" t="e">
-        <f t="shared" ref="O8:O18" si="1">M18/L18*100</f>
+      <c r="O18" s="31" t="e">
+        <f t="shared" ref="O18" si="1">M18/L18*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P18" s="26">
+      <c r="P18" s="25">
         <f>SUM(P6:P17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C19" s="22" t="s">
-        <v>11</v>
+      <c r="C19" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="19"/>
@@ -3545,20 +3484,20 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
       <c r="K19" s="18"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="37"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="P4:P5"/>
-    <mergeCell ref="C3:O3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:O5"/>
+    <mergeCell ref="J3:L3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3571,6 +3510,5 @@
     <ignoredError sqref="D18:J18" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/public/report/YearReport.xlsx
+++ b/public/report/YearReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_688EAC875B0ECFC4FCCC6F6AF1E04F4A83042F76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85B181CC-9D9F-412E-8CFF-303190E6F7C6}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_688EAC875B0ECFC4FCCC6F6AF1E04F4A83042F76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BAA725A-10A7-4DC2-9005-34E5DC49B42E}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-190" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="年報" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>花蓮和平10MW</t>
-  </si>
   <si>
     <t>E-dReg</t>
   </si>
@@ -88,6 +85,10 @@
 (KWh)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>花蓮和平10MW 地號4-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -95,7 +96,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.0"/>
-    <numFmt numFmtId="178" formatCode="0.0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -868,6 +869,105 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -908,105 +1008,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1319,7 +1320,8 @@
   <cols>
     <col min="1" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1332,343 +1334,343 @@
     <row r="2" spans="3:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
+      <c r="D3" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="10" t="s">
-        <v>0</v>
-      </c>
+      <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="53"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="10" t="s">
         <v>1</v>
-      </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="10" t="s">
-        <v>2</v>
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="11"/>
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="3:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="61"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="51" t="s">
         <v>13</v>
-      </c>
-      <c r="M4" s="28"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="3:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="23"/>
-      <c r="D5" s="62">
+      <c r="C5" s="56"/>
+      <c r="D5" s="48">
         <v>1</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="49">
         <v>0.8</v>
       </c>
-      <c r="F5" s="63">
+      <c r="F5" s="49">
         <v>0.6</v>
       </c>
-      <c r="G5" s="63">
+      <c r="G5" s="49">
         <v>0.4</v>
       </c>
-      <c r="H5" s="63">
+      <c r="H5" s="49">
         <v>0.2</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="49">
         <v>0</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="50">
         <v>-1</v>
       </c>
       <c r="K5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="N5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="19"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="52"/>
     </row>
     <row r="6" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="37"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="23"/>
     </row>
     <row r="7" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="6">
         <v>2</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="43"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29"/>
     </row>
     <row r="8" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="6">
         <v>3</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="43"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
     </row>
     <row r="9" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="6">
         <v>4</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="43"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="29"/>
     </row>
     <row r="10" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="6">
         <v>5</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="43"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="29"/>
     </row>
     <row r="11" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="6">
         <v>6</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="44"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="6">
         <v>7</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="45"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="31"/>
     </row>
     <row r="13" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="6">
         <v>8</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="43"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="29"/>
     </row>
     <row r="14" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="6">
         <v>9</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="44"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="30"/>
     </row>
     <row r="15" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="6">
         <v>10</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="43"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="29"/>
     </row>
     <row r="16" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="6">
         <v>11</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="43"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="29"/>
     </row>
     <row r="17" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="6">
         <v>12</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="49"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="35"/>
     </row>
     <row r="18" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="56"/>
-      <c r="P18" s="57"/>
+        <v>9</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="43"/>
     </row>
     <row r="19" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="49"/>
+        <v>10</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/public/report/YearReport.xlsx
+++ b/public/report/YearReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_688EAC875B0ECFC4FCCC6F6AF1E04F4A83042F76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BAA725A-10A7-4DC2-9005-34E5DC49B42E}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_688EAC875B0ECFC4FCCC6F6AF1E04F4A83042F76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03171742-483D-44B8-B04F-989DF65C2724}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,16 +77,16 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>總用電量 (KWh)</t>
+    <t>花蓮和平10MW 地號4-1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>輔助用電
-(KWh)</t>
+    <t>總用電量 (MWh)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>花蓮和平10MW 地號4-1</t>
+    <t>總輔助用電量
+(KWh)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -98,7 +98,7 @@
     <numFmt numFmtId="176" formatCode="#,##0.0"/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,12 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -830,18 +836,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1008,6 +1002,18 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1327,350 +1333,350 @@
     <col min="11" max="11" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="3:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="53"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="10" t="s">
+      <c r="J3" s="49"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="12"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" spans="3:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="13" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="61"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63" t="s">
+      <c r="L4" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="57"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="51" t="s">
-        <v>13</v>
+      <c r="P4" s="47" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="3:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="56"/>
-      <c r="D5" s="48">
+      <c r="C5" s="52"/>
+      <c r="D5" s="44">
         <v>1</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="45">
         <v>0.8</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="45">
         <v>0.6</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="45">
         <v>0.4</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="45">
         <v>0.2</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="45">
         <v>0</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="46">
         <v>-1</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="N5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="64"/>
-      <c r="P5" s="52"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="48"/>
     </row>
     <row r="6" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="5">
+      <c r="C6" s="61">
         <v>1</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="23"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="19"/>
     </row>
     <row r="7" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="6">
+      <c r="C7" s="62">
         <v>2</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="29"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="25"/>
     </row>
     <row r="8" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="6">
+      <c r="C8" s="62">
         <v>3</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="29"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="25"/>
     </row>
     <row r="9" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="6">
+      <c r="C9" s="62">
         <v>4</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="29"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="25"/>
     </row>
     <row r="10" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="6">
+      <c r="C10" s="62">
         <v>5</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="29"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="25"/>
     </row>
     <row r="11" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="6">
+      <c r="C11" s="62">
         <v>6</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="30"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="26"/>
     </row>
     <row r="12" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="6">
+      <c r="C12" s="62">
         <v>7</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="31"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="27"/>
     </row>
     <row r="13" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="6">
+      <c r="C13" s="62">
         <v>8</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="29"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="25"/>
     </row>
     <row r="14" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="6">
+      <c r="C14" s="62">
         <v>9</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="30"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="26"/>
     </row>
     <row r="15" spans="3:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="6">
+      <c r="C15" s="62">
         <v>10</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="29"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="25"/>
     </row>
     <row r="16" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="6">
+      <c r="C16" s="62">
         <v>11</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="29"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25"/>
     </row>
     <row r="17" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="6">
+      <c r="C17" s="62">
         <v>12</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="35"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="31"/>
     </row>
     <row r="18" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="43"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="39"/>
     </row>
     <row r="19" spans="3:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="35"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="6">
